--- a/TEMPDOC.xlsx
+++ b/TEMPDOC.xlsx
@@ -38,115 +38,115 @@
     <t xml:space="preserve">Cum.Wt</t>
   </si>
   <si>
-    <t xml:space="preserve">Rich_E_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GGC_GS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_GGC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_GGC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_GC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GGC_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GC_GGC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GGC_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GGC_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_GS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GC_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_GC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GC_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GGC_WE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_E_WE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GC_GS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_C_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GS_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GC_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_C_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_GS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GS_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_LS_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GC_WE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_GS_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_WE_LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_WE_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_H_WE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_WE_LS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich_WE_GS</t>
+    <t xml:space="preserve">TG_B_GC_GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_WE_GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GS_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GGC_GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GS_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GS_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GC_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GC_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GC_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GC_GGC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GGC_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GC_WE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_WE_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_C_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_C_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_LS_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GGC_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_GGC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GGC_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_GGC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_WE_LC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_WE_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_H_WE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_GGC_WE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG_B_E_WE</t>
   </si>
 </sst>
 </file>
@@ -506,10 +506,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>403.044633865885</v>
+        <v>71.5265521338028</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -518,13 +518,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.179074011236013</v>
+        <v>0.478484431911132</v>
       </c>
       <c r="G2" t="n">
-        <v>-194.930767637168</v>
+        <v>-31.399639703265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.179074011236013</v>
+        <v>0.478484431911132</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>403.155071178031</v>
+        <v>73.5394453203033</v>
       </c>
       <c r="D3" t="n">
-        <v>0.11043731214653</v>
+        <v>2.01289318650052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.946278215851934</v>
+        <v>0.365515499919764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.169453835857863</v>
+        <v>0.174893476333821</v>
       </c>
       <c r="G3" t="n">
-        <v>-196.160868922349</v>
+        <v>-32.4060862965153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.348527847093876</v>
+        <v>0.653377908244953</v>
       </c>
     </row>
     <row r="4">
@@ -558,25 +558,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>403.850275213259</v>
+        <v>74.9475326062837</v>
       </c>
       <c r="D4" t="n">
-        <v>0.805641347373694</v>
+        <v>3.42098047248092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.668431956014776</v>
+        <v>0.180777147381251</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1196987916019</v>
+        <v>0.0864990506672326</v>
       </c>
       <c r="G4" t="n">
-        <v>-195.333588310855</v>
+        <v>-29.3968432262188</v>
       </c>
       <c r="H4" t="n">
-        <v>0.468226638695776</v>
+        <v>0.739876958912186</v>
       </c>
     </row>
     <row r="5">
@@ -584,25 +584,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>403.909490630702</v>
+        <v>75.0785779597615</v>
       </c>
       <c r="D5" t="n">
-        <v>0.86485676481675</v>
+        <v>3.55202582595876</v>
       </c>
       <c r="E5" t="n">
-        <v>0.648931326369008</v>
+        <v>0.169311864428725</v>
       </c>
       <c r="F5" t="n">
-        <v>0.116206735629604</v>
+        <v>0.0810130912669928</v>
       </c>
       <c r="G5" t="n">
-        <v>-196.538078648684</v>
+        <v>-33.1756526162444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.58443337432538</v>
+        <v>0.820890050179178</v>
       </c>
     </row>
     <row r="6">
@@ -610,25 +610,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>404.363380528738</v>
+        <v>75.5511029787754</v>
       </c>
       <c r="D6" t="n">
-        <v>1.31874666285353</v>
+        <v>4.02455084497262</v>
       </c>
       <c r="E6" t="n">
-        <v>0.517175330488512</v>
+        <v>0.133684140428976</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0926126609428883</v>
+        <v>0.0639657799886865</v>
       </c>
       <c r="G6" t="n">
-        <v>-196.765023597703</v>
+        <v>-33.4119151257513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.677046035268268</v>
+        <v>0.884855830167865</v>
       </c>
     </row>
     <row r="7">
@@ -636,25 +636,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>405.696332613942</v>
+        <v>75.6285292862078</v>
       </c>
       <c r="D7" t="n">
-        <v>2.65169874805736</v>
+        <v>4.10197715240503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.265577288811534</v>
+        <v>0.128607702210171</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0475579904006665</v>
+        <v>0.0615367833314297</v>
       </c>
       <c r="G7" t="n">
-        <v>-197.431499640304</v>
+        <v>-33.4506282794675</v>
       </c>
       <c r="H7" t="n">
-        <v>0.724604025668935</v>
+        <v>0.946392613499295</v>
       </c>
     </row>
     <row r="8">
@@ -662,25 +662,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>406.261374865294</v>
+        <v>76.5126120156344</v>
       </c>
       <c r="D8" t="n">
-        <v>3.21674099940918</v>
+        <v>4.98605988183164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.200213596523445</v>
+        <v>0.0826591344702442</v>
       </c>
       <c r="F8" t="n">
-        <v>0.035853051833442</v>
+        <v>0.0395511089992606</v>
       </c>
       <c r="G8" t="n">
-        <v>-197.71402076598</v>
+        <v>-33.8926696441808</v>
       </c>
       <c r="H8" t="n">
-        <v>0.760457077502377</v>
+        <v>0.985943722498555</v>
       </c>
     </row>
     <row r="9">
@@ -691,22 +691,22 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>406.326542225387</v>
+        <v>78.5827631981326</v>
       </c>
       <c r="D9" t="n">
-        <v>3.28190835950198</v>
+        <v>7.05621106432983</v>
       </c>
       <c r="E9" t="n">
-        <v>0.193795038739799</v>
+        <v>0.0293604857085794</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0347036549447743</v>
+        <v>0.0140485353249045</v>
       </c>
       <c r="G9" t="n">
-        <v>-197.746604446027</v>
+        <v>-33.7358260435107</v>
       </c>
       <c r="H9" t="n">
-        <v>0.795160732447151</v>
+        <v>0.99999225782346</v>
       </c>
     </row>
     <row r="10">
@@ -714,25 +714,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>406.331391417198</v>
+        <v>95.376722371071</v>
       </c>
       <c r="D10" t="n">
-        <v>3.28675755131275</v>
+        <v>23.8501702372682</v>
       </c>
       <c r="E10" t="n">
-        <v>0.193325733250379</v>
+        <v>0.00000662218541995413</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0346196145282887</v>
+        <v>0.00000316861262867693</v>
       </c>
       <c r="G10" t="n">
-        <v>-196.574146412824</v>
+        <v>-43.4143885827958</v>
       </c>
       <c r="H10" t="n">
-        <v>0.82978034697544</v>
+        <v>0.999995426436088</v>
       </c>
     </row>
     <row r="11">
@@ -743,22 +743,22 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>406.583311995285</v>
+        <v>97.5261709457177</v>
       </c>
       <c r="D11" t="n">
-        <v>3.5386781293999</v>
+        <v>25.999618811915</v>
       </c>
       <c r="E11" t="n">
-        <v>0.170445605122431</v>
+        <v>0.00000226076025335722</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0305223782068232</v>
+        <v>0.00000108173858551489</v>
       </c>
       <c r="G11" t="n">
-        <v>-197.874989330976</v>
+        <v>-43.3464188061922</v>
       </c>
       <c r="H11" t="n">
-        <v>0.860302725182263</v>
+        <v>0.999996508174674</v>
       </c>
     </row>
     <row r="12">
@@ -766,25 +766,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>406.604061734913</v>
+        <v>98.9972713473809</v>
       </c>
       <c r="D12" t="n">
-        <v>3.55942786902807</v>
+        <v>27.4707192135782</v>
       </c>
       <c r="E12" t="n">
-        <v>0.168686395722926</v>
+        <v>0.00000108345060347354</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0302073495230497</v>
+        <v>0.000000518414246506812</v>
       </c>
       <c r="G12" t="n">
-        <v>-197.88536420079</v>
+        <v>-45.2246630709507</v>
       </c>
       <c r="H12" t="n">
-        <v>0.890510074705313</v>
+        <v>0.99999702658892</v>
       </c>
     </row>
     <row r="13">
@@ -792,25 +792,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>406.942833004358</v>
+        <v>99.0220599053996</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8981991384731</v>
+        <v>27.4955077715968</v>
       </c>
       <c r="E13" t="n">
-        <v>0.142402237230896</v>
+        <v>0.00000107010489049129</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0255005398299188</v>
+        <v>0.000000512028530612046</v>
       </c>
       <c r="G13" t="n">
-        <v>-198.054749835512</v>
+        <v>-45.2370573499601</v>
       </c>
       <c r="H13" t="n">
-        <v>0.916010614535232</v>
+        <v>0.999997538617451</v>
       </c>
     </row>
     <row r="14">
@@ -818,25 +818,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>406.983758785662</v>
+        <v>99.5107489151315</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9391249197775</v>
+        <v>27.9841967813288</v>
       </c>
       <c r="E14" t="n">
-        <v>0.139517887534285</v>
+        <v>0.000000838125161126261</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0249840277599394</v>
+        <v>0.000000401029841591925</v>
       </c>
       <c r="G14" t="n">
-        <v>-196.900330097057</v>
+        <v>-45.481401854826</v>
       </c>
       <c r="H14" t="n">
-        <v>0.940994642295171</v>
+        <v>0.999997939647293</v>
       </c>
     </row>
     <row r="15">
@@ -844,25 +844,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>409.505527866783</v>
+        <v>99.6457976673187</v>
       </c>
       <c r="D15" t="n">
-        <v>6.46089400089841</v>
+        <v>28.119245533516</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0395398205200623</v>
+        <v>0.00000078339972499272</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00708055426407955</v>
+        <v>0.000000374844572372478</v>
       </c>
       <c r="G15" t="n">
-        <v>-198.161214637617</v>
+        <v>-45.5489262309196</v>
       </c>
       <c r="H15" t="n">
-        <v>0.948075196559251</v>
+        <v>0.999998314491865</v>
       </c>
     </row>
     <row r="16">
@@ -870,25 +870,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>409.719067329965</v>
+        <v>99.664734310811</v>
       </c>
       <c r="D16" t="n">
-        <v>6.67443346408055</v>
+        <v>28.1381821770082</v>
       </c>
       <c r="E16" t="n">
-        <v>0.035535725655669</v>
+        <v>0.000000776017249320765</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00636352493534313</v>
+        <v>0.000000371312172694485</v>
       </c>
       <c r="G16" t="n">
-        <v>-198.267984369208</v>
+        <v>-45.5583945526658</v>
       </c>
       <c r="H16" t="n">
-        <v>0.954438721494594</v>
+        <v>0.999998685804038</v>
       </c>
     </row>
     <row r="17">
@@ -896,25 +896,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>409.872093443213</v>
+        <v>100.201080253066</v>
       </c>
       <c r="D17" t="n">
-        <v>6.82745957732834</v>
+        <v>28.6745281192636</v>
       </c>
       <c r="E17" t="n">
-        <v>0.032918193219223</v>
+        <v>0.000000593478968670367</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00589479290240837</v>
+        <v>0.000000283970447175445</v>
       </c>
       <c r="G17" t="n">
-        <v>-201.773884559444</v>
+        <v>-42.3005401265332</v>
       </c>
       <c r="H17" t="n">
-        <v>0.960333514397002</v>
+        <v>0.999998969774485</v>
       </c>
     </row>
     <row r="18">
@@ -922,25 +922,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>410.125582342569</v>
+        <v>101.124702118578</v>
       </c>
       <c r="D18" t="n">
-        <v>7.08094847668451</v>
+        <v>29.5981499847748</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0289995711121203</v>
+        <v>0.000000373975708420957</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00519306952317138</v>
+        <v>0.000000178941554392364</v>
       </c>
       <c r="G18" t="n">
-        <v>-199.646124504618</v>
+        <v>-42.7623510592888</v>
       </c>
       <c r="H18" t="n">
-        <v>0.965526583920173</v>
+        <v>0.999999148716039</v>
       </c>
     </row>
     <row r="19">
@@ -948,25 +948,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>410.225774557802</v>
+        <v>101.725336784945</v>
       </c>
       <c r="D19" t="n">
-        <v>7.18114069191677</v>
+        <v>30.1987846511424</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0275825943149737</v>
+        <v>0.000000276960116308637</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00493932580427798</v>
+        <v>0.000000132521103913979</v>
       </c>
       <c r="G19" t="n">
-        <v>-199.696220612234</v>
+        <v>-46.5886957897328</v>
       </c>
       <c r="H19" t="n">
-        <v>0.970465909724451</v>
+        <v>0.999999281237143</v>
       </c>
     </row>
     <row r="20">
@@ -974,25 +974,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>410.551182657264</v>
+        <v>101.832452386599</v>
       </c>
       <c r="D20" t="n">
-        <v>7.50654879137886</v>
+        <v>30.3059002527967</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0234408653875808</v>
+        <v>0.000000262516965533775</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00419764979179751</v>
+        <v>0.000000125610281120462</v>
       </c>
       <c r="G20" t="n">
-        <v>-199.858924661965</v>
+        <v>-46.64225359056</v>
       </c>
       <c r="H20" t="n">
-        <v>0.974663559516249</v>
+        <v>0.999999406847424</v>
       </c>
     </row>
     <row r="21">
@@ -1000,25 +1000,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>410.554694932136</v>
+        <v>101.980304046903</v>
       </c>
       <c r="D21" t="n">
-        <v>7.51006106625118</v>
+        <v>30.4537519131007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0233997361312214</v>
+        <v>0.00000024381015773606</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00419028461088207</v>
+        <v>0.000000116659364818502</v>
       </c>
       <c r="G21" t="n">
-        <v>-196.233869205198</v>
+        <v>-46.716179420712</v>
       </c>
       <c r="H21" t="n">
-        <v>0.978853844127131</v>
+        <v>0.999999523506789</v>
       </c>
     </row>
     <row r="22">
@@ -1026,25 +1026,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>411.358646865547</v>
+        <v>102.139468886266</v>
       </c>
       <c r="D22" t="n">
-        <v>8.3140129996624</v>
+        <v>30.612916752463</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0156543491470825</v>
+        <v>0.000000225159144420441</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00280328709505712</v>
+        <v>0.000000107735145307611</v>
       </c>
       <c r="G22" t="n">
-        <v>-196.635845171904</v>
+        <v>-48.9897344431329</v>
       </c>
       <c r="H22" t="n">
-        <v>0.981657131222188</v>
+        <v>0.999999631241934</v>
       </c>
     </row>
     <row r="23">
@@ -1052,25 +1052,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>411.415748376008</v>
+        <v>103.889081348453</v>
       </c>
       <c r="D23" t="n">
-        <v>8.37111451012265</v>
+        <v>32.3625292146499</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0152137256536711</v>
+        <v>0.0000000938784846612274</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00272438287864711</v>
+        <v>0.0000000449193934018053</v>
       </c>
       <c r="G23" t="n">
-        <v>-199.116324892229</v>
+        <v>-46.5278740075596</v>
       </c>
       <c r="H23" t="n">
-        <v>0.984381514100835</v>
+        <v>0.999999676161328</v>
       </c>
     </row>
     <row r="24">
@@ -1078,25 +1078,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>411.550644644341</v>
+        <v>104.116991205696</v>
       </c>
       <c r="D24" t="n">
-        <v>8.5060107784559</v>
+        <v>32.5904390718931</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0142214286894564</v>
+        <v>0.0000000837676002612891</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00254668828092787</v>
+        <v>0.0000000400814926235817</v>
       </c>
       <c r="G24" t="n">
-        <v>-199.183773026396</v>
+        <v>-46.6418289361813</v>
       </c>
       <c r="H24" t="n">
-        <v>0.986928202381763</v>
+        <v>0.99999971624282</v>
       </c>
     </row>
     <row r="25">
@@ -1104,25 +1104,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>411.986965853243</v>
+        <v>104.572598616878</v>
       </c>
       <c r="D25" t="n">
-        <v>8.94233198735782</v>
+        <v>33.0460464830755</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0114339761311091</v>
+        <v>0.0000000667025108011445</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00204752797017453</v>
+        <v>0.0000000319161129877318</v>
       </c>
       <c r="G25" t="n">
-        <v>-198.193482926621</v>
+        <v>-46.8696326417725</v>
       </c>
       <c r="H25" t="n">
-        <v>0.988975730351938</v>
+        <v>0.999999748158933</v>
       </c>
     </row>
     <row r="26">
@@ -1130,25 +1130,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>412.050880084829</v>
+        <v>104.755161404084</v>
       </c>
       <c r="D26" t="n">
-        <v>9.00624621894406</v>
+        <v>33.2286092702815</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0110743560471084</v>
+        <v>0.0000000608834391019303</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00198312935921149</v>
+        <v>0.0000000291317777714831</v>
       </c>
       <c r="G26" t="n">
-        <v>-200.608773375748</v>
+        <v>-48.1036080993024</v>
       </c>
       <c r="H26" t="n">
-        <v>0.990958859711149</v>
+        <v>0.999999777290711</v>
       </c>
     </row>
     <row r="27">
@@ -1159,22 +1159,22 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>412.510364988294</v>
+        <v>104.929713390133</v>
       </c>
       <c r="D27" t="n">
-        <v>9.46573112240912</v>
+        <v>33.40316125633</v>
       </c>
       <c r="E27" t="n">
-        <v>0.008801214451175</v>
+        <v>0.0000000557950529575014</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00157606877552027</v>
+        <v>0.0000000266970642178216</v>
       </c>
       <c r="G27" t="n">
-        <v>-200.83851582748</v>
+        <v>-47.0481900283997</v>
       </c>
       <c r="H27" t="n">
-        <v>0.992534928486669</v>
+        <v>0.999999803987775</v>
       </c>
     </row>
     <row r="28">
@@ -1182,25 +1182,25 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>412.562795599461</v>
+        <v>105.004848370386</v>
       </c>
       <c r="D28" t="n">
-        <v>9.51816173357656</v>
+        <v>33.4782962365829</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00857348595282119</v>
+        <v>0.0000000537378566479735</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0015352885198473</v>
+        <v>0.0000000257127278103274</v>
       </c>
       <c r="G28" t="n">
-        <v>-200.864731133064</v>
+        <v>-48.2284515824531</v>
       </c>
       <c r="H28" t="n">
-        <v>0.994070217006517</v>
+        <v>0.999999829700503</v>
       </c>
     </row>
     <row r="29">
@@ -1208,25 +1208,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>413.139939170026</v>
+        <v>105.233413388477</v>
       </c>
       <c r="D29" t="n">
-        <v>10.0953053041415</v>
+        <v>33.7068612546746</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006424396053523</v>
+        <v>0.0000000479344862871986</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00115044237107317</v>
+        <v>0.0000000229359054400821</v>
       </c>
       <c r="G29" t="n">
-        <v>-199.978420289239</v>
+        <v>-47.200040027572</v>
       </c>
       <c r="H29" t="n">
-        <v>0.99522065937759</v>
+        <v>0.999999852636409</v>
       </c>
     </row>
     <row r="30">
@@ -1234,25 +1234,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>413.325968992518</v>
+        <v>105.376544556521</v>
       </c>
       <c r="D30" t="n">
-        <v>10.2813351266329</v>
+        <v>33.8499924227185</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00585378063948606</v>
+        <v>0.0000000446239015908918</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00104825998000848</v>
+        <v>0.0000000213518422023761</v>
       </c>
       <c r="G30" t="n">
-        <v>-200.071435200484</v>
+        <v>-48.4142996755209</v>
       </c>
       <c r="H30" t="n">
-        <v>0.996268919357598</v>
+        <v>0.999999873988251</v>
       </c>
     </row>
     <row r="31">
@@ -1260,25 +1260,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>413.474998638983</v>
+        <v>105.415194658301</v>
       </c>
       <c r="D31" t="n">
-        <v>10.4303647730982</v>
+        <v>33.8886425244981</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00543344239929503</v>
+        <v>0.0000000437698215717205</v>
       </c>
       <c r="F31" t="n">
-        <v>0.000972988325261586</v>
+        <v>0.0000000209431782095963</v>
       </c>
       <c r="G31" t="n">
-        <v>-200.145950023717</v>
+        <v>-43.6641190682809</v>
       </c>
       <c r="H31" t="n">
-        <v>0.99724190768286</v>
+        <v>0.999999894931429</v>
       </c>
     </row>
     <row r="32">
@@ -1286,25 +1286,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>414.257349926452</v>
+        <v>105.493522220539</v>
       </c>
       <c r="D32" t="n">
-        <v>11.2127160605669</v>
+        <v>33.9669700867362</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00367442717107303</v>
+        <v>0.0000000420887630265736</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000657994412518642</v>
+        <v>0.0000000201388178666123</v>
       </c>
       <c r="G32" t="n">
-        <v>-198.085196702356</v>
+        <v>-48.4727885075298</v>
       </c>
       <c r="H32" t="n">
-        <v>0.997899902095379</v>
+        <v>0.999999915070247</v>
       </c>
     </row>
     <row r="33">
@@ -1312,25 +1312,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>414.402759351703</v>
+        <v>105.542499131505</v>
       </c>
       <c r="D33" t="n">
-        <v>11.3581254858182</v>
+        <v>34.015946997702</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00341675932504186</v>
+        <v>0.0000000410705918281786</v>
       </c>
       <c r="F33" t="n">
-        <v>0.000611852797763297</v>
+        <v>0.00000001965163879916</v>
       </c>
       <c r="G33" t="n">
-        <v>-200.609830380077</v>
+        <v>-48.4972769630126</v>
       </c>
       <c r="H33" t="n">
-        <v>0.998511754893142</v>
+        <v>0.999999934721886</v>
       </c>
     </row>
     <row r="34">
@@ -1338,25 +1338,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>414.692088150355</v>
+        <v>105.964308306091</v>
       </c>
       <c r="D34" t="n">
-        <v>11.6474542844705</v>
+        <v>34.4377561722881</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0029565650450995</v>
+        <v>0.0000000332610735515946</v>
       </c>
       <c r="F34" t="n">
-        <v>0.000529443962106151</v>
+        <v>0.0000000159149058830891</v>
       </c>
       <c r="G34" t="n">
-        <v>-197.022514663413</v>
+        <v>-45.1821541530455</v>
       </c>
       <c r="H34" t="n">
-        <v>0.999041198855248</v>
+        <v>0.999999950636792</v>
       </c>
     </row>
     <row r="35">
@@ -1364,25 +1364,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>415.458413953853</v>
+        <v>106.006918321664</v>
       </c>
       <c r="D35" t="n">
-        <v>12.4137800879681</v>
+        <v>34.4803661878611</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00201549583078741</v>
+        <v>0.0000000325599414533151</v>
       </c>
       <c r="F35" t="n">
-        <v>0.000360922923048562</v>
+        <v>0.0000000155794250893492</v>
       </c>
       <c r="G35" t="n">
-        <v>-198.685728716057</v>
+        <v>-48.7294865580922</v>
       </c>
       <c r="H35" t="n">
-        <v>0.999402121778297</v>
+        <v>0.999999966216217</v>
       </c>
     </row>
     <row r="36">
@@ -1390,25 +1390,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>416.04394634587</v>
+        <v>106.53171717104</v>
       </c>
       <c r="D36" t="n">
-        <v>12.9993124799852</v>
+        <v>35.005165037237</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00150395610408729</v>
+        <v>0.0000000250452281990156</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000269319452281796</v>
+        <v>0.0000000119837517868906</v>
       </c>
       <c r="G36" t="n">
-        <v>-198.978494912065</v>
+        <v>-45.4658585855199</v>
       </c>
       <c r="H36" t="n">
-        <v>0.999671441230578</v>
+        <v>0.999999978199968</v>
       </c>
     </row>
     <row r="37">
@@ -1416,25 +1416,25 @@
         <v>43</v>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>416.894818318334</v>
+        <v>106.576996982143</v>
       </c>
       <c r="D37" t="n">
-        <v>13.8501844524491</v>
+        <v>35.05044484834</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000982812472885067</v>
+        <v>0.0000000244845770894803</v>
       </c>
       <c r="F37" t="n">
-        <v>0.000175996171812314</v>
+        <v>0.0000000117154889592443</v>
       </c>
       <c r="G37" t="n">
-        <v>-199.403930898297</v>
+        <v>-45.4884984910714</v>
       </c>
       <c r="H37" t="n">
-        <v>0.999847437402391</v>
+        <v>0.999999989915457</v>
       </c>
     </row>
     <row r="38">
@@ -1442,22 +1442,22 @@
         <v>44</v>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>417.1805928299</v>
+        <v>106.876812996459</v>
       </c>
       <c r="D38" t="n">
-        <v>14.1359589640147</v>
+        <v>35.3502608626565</v>
       </c>
       <c r="E38" t="n">
-        <v>0.000851952757166579</v>
+        <v>0.0000000210760095531439</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0001525625976094</v>
+        <v>0.0000000100845424579896</v>
       </c>
       <c r="G38" t="n">
-        <v>-198.266767003185</v>
+        <v>-45.6384064982297</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
